--- a/data/trans_bre/IP11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,15</t>
+          <t>-4,8; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 1,27</t>
+          <t>-9,59; 0,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,55</t>
+          <t>-6,96; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,7</t>
+          <t>-1,47; 4,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 116,65</t>
+          <t>-41,38; 99,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 19,58</t>
+          <t>-69,74; 14,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 90,98</t>
+          <t>-70,31; 75,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 691,28</t>
+          <t>-68,53; 709,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 0,35</t>
+          <t>-6,23; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 6,19</t>
+          <t>-2,82; 6,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,64</t>
+          <t>-3,54; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,52</t>
+          <t>-2,49; 2,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,34; 10,32</t>
+          <t>-72,5; 17,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 98,98</t>
+          <t>-27,08; 108,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,51; 75,9</t>
+          <t>-55,98; 114,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 299,18</t>
+          <t>-69,61; 261,79</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,86</t>
+          <t>-5,77; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,81</t>
+          <t>-10,7; -0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,12</t>
+          <t>-5,28; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 71,76</t>
+          <t>-67,74; 71,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,65; -5,25</t>
+          <t>-76,46; -10,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 51,01</t>
+          <t>-79,41; 50,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,88; 115,27</t>
+          <t>-75,07; 116,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,58</t>
+          <t>-4,35; 2,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,04</t>
+          <t>-7,77; 0,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; -1,09</t>
+          <t>-7,5; -1,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,3</t>
+          <t>-6,44; 0,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 75,61</t>
+          <t>-65,89; 72,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,82; 19,41</t>
+          <t>-65,36; 18,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-93,77; -15,28</t>
+          <t>-94,03; -21,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,61; 33,13</t>
+          <t>-91,66; 31,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,81</t>
+          <t>-3,28; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,17</t>
+          <t>-4,86; -0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,26</t>
+          <t>-3,93; -0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,03</t>
+          <t>-2,37; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 16,24</t>
+          <t>-43,8; 14,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -1,12</t>
+          <t>-44,18; -1,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -5,16</t>
+          <t>-59,28; -6,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 46,13</t>
+          <t>-56,89; 36,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 6,2</t>
+          <t>-5,07; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 0,89</t>
+          <t>-10,29; 1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 3,01</t>
+          <t>-6,3; 3,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,66</t>
+          <t>-1,28; 4,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 99,57</t>
+          <t>-46,7; 97,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 14,79</t>
+          <t>-72,32; 22,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,31; 75,21</t>
+          <t>-68,27; 78,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 709,61</t>
+          <t>-64,89; 717,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,53</t>
+          <t>-6,21; 0,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 6,8</t>
+          <t>-2,66; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,01</t>
+          <t>-3,85; 2,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,64</t>
+          <t>-2,53; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 17,36</t>
+          <t>-74,32; 18,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 108,06</t>
+          <t>-26,37; 94,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 114,71</t>
+          <t>-59,34; 85,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 261,79</t>
+          <t>-77,3; 262,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,99%</t>
+          <t>-22,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,77</t>
+          <t>-5,44; 2,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -0,94</t>
+          <t>-10,32; -0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 1,17</t>
+          <t>-5,42; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,63</t>
+          <t>-5,37; 2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 71,63</t>
+          <t>-67,86; 103,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-76,46; -10,51</t>
+          <t>-74,81; -7,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 50,91</t>
+          <t>-78,76; 53,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 116,24</t>
+          <t>-77,92; 110,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,63</t>
+          <t>-3,89; 2,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 0,95</t>
+          <t>-7,83; 1,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -1,4</t>
+          <t>-7,78; -1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,12</t>
+          <t>-5,92; -0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 72,89</t>
+          <t>-57,91; 85,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 18,94</t>
+          <t>-65,79; 24,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,03; -21,76</t>
+          <t>-94,16; -25,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,66; 31,05</t>
+          <t>-91,69; 5,39</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,44%</t>
+          <t>-18,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,79</t>
+          <t>-3,21; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,17</t>
+          <t>-5,08; -0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,35</t>
+          <t>-3,85; -0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,88</t>
+          <t>-2,2; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 14,68</t>
+          <t>-43,46; 16,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -1,99</t>
+          <t>-44,58; -2,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -6,11</t>
+          <t>-60,74; -7,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 36,86</t>
+          <t>-55,57; 44,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,96</t>
+          <t>-4,75; 6,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 1,11</t>
+          <t>-9,92; 1,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,03</t>
+          <t>-6,36; 3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,6</t>
+          <t>-1,96; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 97,46</t>
+          <t>-43,22; 116,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 22,76</t>
+          <t>-71,01; 19,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,27; 78,62</t>
+          <t>-70,09; 90,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 717,78</t>
+          <t>-77,9; 636,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,57</t>
+          <t>-6,35; 0,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 6,1</t>
+          <t>-3,08; 6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,6</t>
+          <t>-3,8; 2,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,84</t>
+          <t>-2,66; 2,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,32; 18,88</t>
+          <t>-75,34; 10,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 94,81</t>
+          <t>-29,06; 98,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 85,0</t>
+          <t>-58,51; 75,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,3; 262,9</t>
+          <t>-73,89; 290,11</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,66%</t>
+          <t>-8,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,98</t>
+          <t>-5,52; 2,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -0,85</t>
+          <t>-10,15; -0,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,29</t>
+          <t>-5,42; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,42</t>
+          <t>-4,1; 3,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 103,17</t>
+          <t>-68,87; 71,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,81; -7,33</t>
+          <t>-74,65; -5,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,76; 53,73</t>
+          <t>-77,78; 51,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 110,29</t>
+          <t>-65,65; 159,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-63,11%</t>
+          <t>-61,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,59</t>
+          <t>-4,32; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,44</t>
+          <t>-7,6; 1,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -1,44</t>
+          <t>-7,36; -1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -0,11</t>
+          <t>-5,64; 0,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 85,34</t>
+          <t>-62,04; 75,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 24,82</t>
+          <t>-65,82; 19,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,16; -25,77</t>
+          <t>-93,77; -15,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,69; 5,39</t>
+          <t>-92,35; 42,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>-14,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,85</t>
+          <t>-3,12; 0,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,34</t>
+          <t>-4,91; -0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,35</t>
+          <t>-3,94; -0,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,98</t>
+          <t>-2,09; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 16,85</t>
+          <t>-42,98; 16,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,58; -2,96</t>
+          <t>-44,13; -1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,74; -7,4</t>
+          <t>-60,09; -5,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 44,5</t>
+          <t>-50,96; 51,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,07</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-38,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-22,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.6392103045173431</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.072622438946433</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.539416079398908</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.25275659010872</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.07388943356824519</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3848223034101303</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2273412482752162</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.7128896515956438</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 6,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,92; 1,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,36; 3,55</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,96; 4,64</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-43,22; 116,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-71,01; 19,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-70,09; 90,98</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-77,9; 636,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.754645421476872</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.923532778705567</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.36187102214575</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.964877901812718</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4322298161973386</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7101343113767294</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7008547011714864</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7790076331305084</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.148537758544304</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.268850657466382</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.551831942216331</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.635294028166772</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.166531286587117</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1958439500989014</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.909809652248185</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>6.364172489747638</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,85</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-44,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-12,52%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,35; 0,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 6,19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,8; 2,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 2,7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-75,34; 10,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-29,06; 98,98</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-58,51; 75,9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-73,89; 290,11</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.849768024880837</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.676025274956508</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6201296313440429</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.04929831988837556</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4411751549552904</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1924372349434537</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1251759358429466</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.02009416064546992</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-49,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-39,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,48%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.350906600804652</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.076822220414422</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.802994161848785</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.663881312143255</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7534103689182309</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2905822768641084</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5851132551036926</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7389274976026448</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 2,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,15; -0,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,42; 1,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,1; 3,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-68,87; 71,76</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-74,65; -5,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-77,78; 51,01</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-65,65; 159,38</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3466427516735525</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.188634655077671</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.644833593778301</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.700556831612915</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1032121151845587</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9898061026204511</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7590466404313853</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.901089816750134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,33</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-35,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-74,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-61,36%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.348658963428879</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5.44504048512484</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.872989054631558</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.377854751340772</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2269208707400201</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.498210759642344</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3955684427881986</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08483723792765975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 2,58</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,6; 1,04</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,36; -1,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,64; 0,4</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-62,04; 75,61</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-65,82; 19,41</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-93,77; -15,28</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-92,35; 42,34</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.515677858111355</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.14599842952262</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.415371779462015</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.102813657715304</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6887102045113167</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7464924123820592</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7777742816974214</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.656529205102014</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.861175581158791</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.8141891834110691</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.115746103172221</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.748767441699786</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.7176465484858319</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-0.05252275535998387</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5101015647390795</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.593761343964525</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.8230680562485424</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.334259655654952</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.284901270230296</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.443727285169682</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1600869087557924</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3555528770512805</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.7490227210922252</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.613583506536462</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.320177878370753</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.597294598489992</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.359558570266753</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.638302863755235</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6203699066322496</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.658207863094916</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.93769721810548</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.9235264074284243</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.582296573918363</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.044492897213249</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-1.092745281073405</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.4005709358333075</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7561140331631639</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1940847177675411</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.1527805157624106</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4233542387866822</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-19,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-25,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-39,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-14,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; 0,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; -0,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; -0,26</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 1,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-42,98; 16,24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-44,13; -1,12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-60,09; -5,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,96; 51,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.253783091072896</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.49634625645488</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.148717405378005</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.4452213905791414</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1947556359050085</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2555197408623467</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.392291843862993</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1400291949360195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.122278990810411</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.913528235516504</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.941335189188385</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.087490471059916</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4298390509560215</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4412831495001411</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6008887846541371</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5096413151972139</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8142615853996757</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.1719679193075936</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.2615262235720526</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.156839904508688</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1623988061282724</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.01116460726314879</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.05163889896638876</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.5193755189529268</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
